--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -30,43 +30,40 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Mystical Magical Moonbeam Mark</t>
+  </si>
+  <si>
+    <t>Chris Evans Sweater</t>
+  </si>
+  <si>
+    <t>Flaccillionares</t>
+  </si>
+  <si>
+    <t>Navy MUN</t>
+  </si>
+  <si>
     <t>Center for Student Diversity</t>
   </si>
   <si>
+    <t>bbbbbbbbbbbbbbbbbb</t>
+  </si>
+  <si>
     <t xml:space="preserve">First Empire of NJ </t>
   </si>
   <si>
-    <t>Navy MUN</t>
-  </si>
-  <si>
     <t>Commies</t>
   </si>
   <si>
-    <t>Mystical Magical Moonbeam Mark</t>
-  </si>
-  <si>
     <t>Amy Gold</t>
   </si>
   <si>
-    <t>bbbbbbbbbbbbbbbbbb</t>
-  </si>
-  <si>
-    <t>Chris Evans Sweater</t>
-  </si>
-  <si>
     <t>I Am Peter Awabdeh</t>
   </si>
   <si>
-    <t>Flaccillionares</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.6%</t>
-  </si>
-  <si>
-    <t>42.6%</t>
+    <t>41.7%</t>
   </si>
   <si>
     <t>41.6%</t>
@@ -75,22 +72,22 @@
     <t>40.9%</t>
   </si>
   <si>
-    <t>40.0%</t>
+    <t>40.4%</t>
+  </si>
+  <si>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>39.5%</t>
   </si>
   <si>
     <t>39.1%</t>
   </si>
   <si>
-    <t>38.7%</t>
-  </si>
-  <si>
-    <t>35.7%</t>
-  </si>
-  <si>
-    <t>+129</t>
-  </si>
-  <si>
-    <t>+135</t>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>38.2%</t>
   </si>
   <si>
     <t>+140</t>
@@ -99,16 +96,22 @@
     <t>+144</t>
   </si>
   <si>
-    <t>+150</t>
+    <t>+148</t>
+  </si>
+  <si>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+153</t>
   </si>
   <si>
     <t>+156</t>
   </si>
   <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+180</t>
+    <t>+160</t>
+  </si>
+  <si>
+    <t>+162</t>
   </si>
   <si>
     <t>Probability</t>
@@ -117,91 +120,91 @@
     <t>11.2%</t>
   </si>
   <si>
-    <t>10.7%</t>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>8.7%</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1049</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
   </si>
   <si>
     <t>10.4%</t>
   </si>
   <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+835</t>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+852</t>
   </si>
   <si>
     <t>+862</t>
   </si>
   <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+975</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>12.0%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>+733</t>
-  </si>
-  <si>
     <t>+880</t>
   </si>
   <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+999</t>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+1063</t>
   </si>
 </sst>
 </file>
@@ -587,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -640,10 +643,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -654,10 +657,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -696,10 +699,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -710,10 +713,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -742,114 +745,114 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -860,24 +863,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -906,21 +909,21 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -929,119 +932,119 @@
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -30,88 +30,88 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Commies</t>
+  </si>
+  <si>
+    <t>I Am Peter Awabdeh</t>
+  </si>
+  <si>
+    <t>Chris Evans Sweater</t>
+  </si>
+  <si>
+    <t>Flaccillionares</t>
+  </si>
+  <si>
+    <t>Amy Gold</t>
+  </si>
+  <si>
+    <t>Center for Student Diversity</t>
+  </si>
+  <si>
+    <t>bbbbbbbbbbbbbbbbbb</t>
+  </si>
+  <si>
+    <t>Navy MUN</t>
+  </si>
+  <si>
     <t>Mystical Magical Moonbeam Mark</t>
   </si>
   <si>
-    <t>Chris Evans Sweater</t>
-  </si>
-  <si>
-    <t>Flaccillionares</t>
-  </si>
-  <si>
-    <t>Navy MUN</t>
-  </si>
-  <si>
-    <t>Center for Student Diversity</t>
-  </si>
-  <si>
-    <t>bbbbbbbbbbbbbbbbbb</t>
-  </si>
-  <si>
     <t xml:space="preserve">First Empire of NJ </t>
   </si>
   <si>
-    <t>Commies</t>
-  </si>
-  <si>
-    <t>Amy Gold</t>
-  </si>
-  <si>
-    <t>I Am Peter Awabdeh</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>41.7%</t>
+    <t>43.9%</t>
   </si>
   <si>
     <t>41.6%</t>
   </si>
   <si>
-    <t>40.9%</t>
-  </si>
-  <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>39.5%</t>
-  </si>
-  <si>
-    <t>39.1%</t>
-  </si>
-  <si>
-    <t>38.5%</t>
-  </si>
-  <si>
-    <t>38.2%</t>
+    <t>41.3%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>39.0%</t>
+  </si>
+  <si>
+    <t>38.8%</t>
+  </si>
+  <si>
+    <t>38.7%</t>
+  </si>
+  <si>
+    <t>36.8%</t>
+  </si>
+  <si>
+    <t>+128</t>
   </si>
   <si>
     <t>+140</t>
   </si>
   <si>
-    <t>+144</t>
-  </si>
-  <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+153</t>
+    <t>+142</t>
+  </si>
+  <si>
+    <t>+150</t>
+  </si>
+  <si>
+    <t>+151</t>
   </si>
   <si>
     <t>+156</t>
   </si>
   <si>
-    <t>+160</t>
-  </si>
-  <si>
-    <t>+162</t>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+172</t>
   </si>
   <si>
     <t>Probability</t>
@@ -120,91 +120,91 @@
     <t>11.2%</t>
   </si>
   <si>
-    <t>10.8%</t>
+    <t>10.9%</t>
   </si>
   <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.3%</t>
+    <t>10.1%</t>
   </si>
   <si>
     <t>9.9%</t>
   </si>
   <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
     <t>9.8%</t>
   </si>
   <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+910</t>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>+755</t>
+  </si>
+  <si>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+900</t>
   </si>
   <si>
     <t>+920</t>
   </si>
   <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1049</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+953</t>
-  </si>
-  <si>
-    <t>+1063</t>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>+1036</t>
   </si>
 </sst>
 </file>
@@ -604,7 +604,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -618,7 +618,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -632,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -646,7 +646,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -660,7 +660,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -674,7 +674,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -688,7 +688,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -745,7 +745,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -754,12 +754,12 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -768,12 +768,12 @@
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -782,12 +782,12 @@
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -796,7 +796,7 @@
         <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -807,15 +807,15 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -824,63 +824,63 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -909,41 +909,41 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
         <v>58</v>
@@ -951,16 +951,16 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -971,77 +971,77 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>

--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t>Record</t>
   </si>
@@ -33,100 +33,133 @@
     <t>Commies</t>
   </si>
   <si>
+    <t>Navy MUN</t>
+  </si>
+  <si>
+    <t>Chris Evans Sweater</t>
+  </si>
+  <si>
+    <t>bbbbbbbbbbbbbbbbbb</t>
+  </si>
+  <si>
     <t>I Am Peter Awabdeh</t>
   </si>
   <si>
-    <t>Chris Evans Sweater</t>
+    <t xml:space="preserve">First Empire of NJ </t>
   </si>
   <si>
     <t>Flaccillionares</t>
   </si>
   <si>
+    <t>Center for Student Diversity</t>
+  </si>
+  <si>
     <t>Amy Gold</t>
   </si>
   <si>
-    <t>Center for Student Diversity</t>
-  </si>
-  <si>
-    <t>bbbbbbbbbbbbbbbbbb</t>
-  </si>
-  <si>
-    <t>Navy MUN</t>
-  </si>
-  <si>
     <t>Mystical Magical Moonbeam Mark</t>
   </si>
   <si>
-    <t xml:space="preserve">First Empire of NJ </t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.9%</t>
-  </si>
-  <si>
-    <t>41.6%</t>
+    <t>42.3%</t>
   </si>
   <si>
     <t>41.3%</t>
   </si>
   <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>39.9%</t>
-  </si>
-  <si>
-    <t>39.0%</t>
-  </si>
-  <si>
-    <t>38.8%</t>
-  </si>
-  <si>
-    <t>38.7%</t>
-  </si>
-  <si>
-    <t>36.8%</t>
-  </si>
-  <si>
-    <t>+128</t>
-  </si>
-  <si>
-    <t>+140</t>
+    <t>40.8%</t>
+  </si>
+  <si>
+    <t>40.2%</t>
+  </si>
+  <si>
+    <t>40.1%</t>
+  </si>
+  <si>
+    <t>38.9%</t>
+  </si>
+  <si>
+    <t>37.5%</t>
+  </si>
+  <si>
+    <t>+136</t>
   </si>
   <si>
     <t>+142</t>
   </si>
   <si>
-    <t>+150</t>
-  </si>
-  <si>
-    <t>+151</t>
-  </si>
-  <si>
-    <t>+156</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+172</t>
+    <t>+145</t>
+  </si>
+  <si>
+    <t>+149</t>
+  </si>
+  <si>
+    <t>+157</t>
+  </si>
+  <si>
+    <t>+167</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
+    <t>11.3%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>+785</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>10.8%</t>
   </si>
   <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.1%</t>
+    <t>10.2%</t>
   </si>
   <si>
     <t>9.9%</t>
@@ -135,22 +168,19 @@
     <t>9.5%</t>
   </si>
   <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+817</t>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
+  </si>
+  <si>
+    <t>+826</t>
   </si>
   <si>
     <t>+843</t>
   </si>
   <si>
-    <t>+890</t>
+    <t>+880</t>
   </si>
   <si>
     <t>+910</t>
@@ -159,52 +189,10 @@
     <t>+953</t>
   </si>
   <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>+755</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
     <t>+1036</t>
+  </si>
+  <si>
+    <t>+1105</t>
   </si>
 </sst>
 </file>
@@ -590,7 +578,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -604,7 +592,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -615,10 +603,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -629,10 +617,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -646,7 +634,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -660,7 +648,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -671,10 +659,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -685,10 +673,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -699,10 +687,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -713,10 +701,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -745,16 +733,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -765,94 +753,94 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -863,24 +851,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -909,58 +897,58 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -971,10 +959,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -985,38 +973,38 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1027,24 +1015,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>Record</t>
   </si>
@@ -30,58 +30,73 @@
     <t>Team</t>
   </si>
   <si>
+    <t>I Am Peter Awabdeh</t>
+  </si>
+  <si>
+    <t>Navy MUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Empire of NJ </t>
+  </si>
+  <si>
     <t>Commies</t>
   </si>
   <si>
-    <t>Navy MUN</t>
-  </si>
-  <si>
     <t>Chris Evans Sweater</t>
   </si>
   <si>
+    <t>Amy Gold</t>
+  </si>
+  <si>
     <t>bbbbbbbbbbbbbbbbbb</t>
   </si>
   <si>
-    <t>I Am Peter Awabdeh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Empire of NJ </t>
+    <t>Center for Student Diversity</t>
+  </si>
+  <si>
+    <t>Mystical Magical Moonbeam Mark</t>
   </si>
   <si>
     <t>Flaccillionares</t>
   </si>
   <si>
-    <t>Center for Student Diversity</t>
-  </si>
-  <si>
-    <t>Amy Gold</t>
-  </si>
-  <si>
-    <t>Mystical Magical Moonbeam Mark</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
+    <t>42.9%</t>
+  </si>
+  <si>
+    <t>42.6%</t>
+  </si>
+  <si>
     <t>42.3%</t>
   </si>
   <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>40.8%</t>
+    <t>41.4%</t>
   </si>
   <si>
     <t>40.2%</t>
   </si>
   <si>
-    <t>40.1%</t>
-  </si>
-  <si>
-    <t>38.9%</t>
-  </si>
-  <si>
-    <t>37.5%</t>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>38.1%</t>
+  </si>
+  <si>
+    <t>37.9%</t>
+  </si>
+  <si>
+    <t>37.7%</t>
+  </si>
+  <si>
+    <t>37.0%</t>
+  </si>
+  <si>
+    <t>+133</t>
+  </si>
+  <si>
+    <t>+135</t>
   </si>
   <si>
     <t>+136</t>
@@ -90,109 +105,109 @@
     <t>+142</t>
   </si>
   <si>
-    <t>+145</t>
-  </si>
-  <si>
     <t>+149</t>
   </si>
   <si>
-    <t>+157</t>
-  </si>
-  <si>
-    <t>+167</t>
+    <t>+151</t>
+  </si>
+  <si>
+    <t>+162</t>
+  </si>
+  <si>
+    <t>+164</t>
+  </si>
+  <si>
+    <t>+165</t>
+  </si>
+  <si>
+    <t>+170</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.3%</t>
+    <t>12.3%</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.3%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+975</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>11.8%</t>
   </si>
   <si>
     <t>11.1%</t>
   </si>
   <si>
-    <t>11.0%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
   </si>
   <si>
     <t>8.9%</t>
   </si>
   <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>+785</t>
+    <t>+747</t>
   </si>
   <si>
     <t>+801</t>
   </si>
   <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+999</t>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+964</t>
   </si>
   <si>
     <t>+1024</t>
-  </si>
-  <si>
-    <t>+1076</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+953</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+1105</t>
   </si>
 </sst>
 </file>
@@ -578,7 +593,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -592,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -603,10 +618,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -617,10 +632,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -631,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -645,10 +660,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -659,10 +674,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -673,10 +688,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -687,10 +702,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -701,10 +716,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -733,16 +748,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -753,52 +768,52 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -809,66 +824,66 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -897,142 +912,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -30,184 +30,181 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Mystical Magical Moonbeam Mark</t>
+  </si>
+  <si>
     <t>I Am Peter Awabdeh</t>
   </si>
   <si>
+    <t>bbbbbbbbbbbbbbbbbb</t>
+  </si>
+  <si>
+    <t>Flaccillionares</t>
+  </si>
+  <si>
+    <t>Center for Student Diversity</t>
+  </si>
+  <si>
+    <t>Chris Evans Sweater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Empire of NJ </t>
+  </si>
+  <si>
+    <t>Amy Gold</t>
+  </si>
+  <si>
     <t>Navy MUN</t>
   </si>
   <si>
-    <t xml:space="preserve">First Empire of NJ </t>
-  </si>
-  <si>
     <t>Commies</t>
   </si>
   <si>
-    <t>Chris Evans Sweater</t>
-  </si>
-  <si>
-    <t>Amy Gold</t>
-  </si>
-  <si>
-    <t>bbbbbbbbbbbbbbbbbb</t>
-  </si>
-  <si>
-    <t>Center for Student Diversity</t>
-  </si>
-  <si>
-    <t>Mystical Magical Moonbeam Mark</t>
-  </si>
-  <si>
-    <t>Flaccillionares</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>42.9%</t>
-  </si>
-  <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>42.3%</t>
-  </si>
-  <si>
-    <t>41.4%</t>
-  </si>
-  <si>
-    <t>40.2%</t>
-  </si>
-  <si>
-    <t>39.9%</t>
-  </si>
-  <si>
-    <t>38.1%</t>
-  </si>
-  <si>
-    <t>37.9%</t>
-  </si>
-  <si>
-    <t>37.7%</t>
-  </si>
-  <si>
-    <t>37.0%</t>
-  </si>
-  <si>
-    <t>+133</t>
-  </si>
-  <si>
-    <t>+135</t>
-  </si>
-  <si>
-    <t>+136</t>
-  </si>
-  <si>
-    <t>+142</t>
-  </si>
-  <si>
-    <t>+149</t>
-  </si>
-  <si>
-    <t>+151</t>
+    <t>43.4%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>40.9%</t>
+  </si>
+  <si>
+    <t>40.4%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>39.3%</t>
+  </si>
+  <si>
+    <t>39.1%</t>
+  </si>
+  <si>
+    <t>39.0%</t>
+  </si>
+  <si>
+    <t>38.2%</t>
+  </si>
+  <si>
+    <t>+130</t>
+  </si>
+  <si>
+    <t>+141</t>
+  </si>
+  <si>
+    <t>+144</t>
+  </si>
+  <si>
+    <t>+148</t>
+  </si>
+  <si>
+    <t>+150</t>
+  </si>
+  <si>
+    <t>+154</t>
+  </si>
+  <si>
+    <t>+156</t>
   </si>
   <si>
     <t>+162</t>
   </si>
   <si>
-    <t>+164</t>
-  </si>
-  <si>
-    <t>+165</t>
-  </si>
-  <si>
-    <t>+170</t>
-  </si>
-  <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>12.3%</t>
-  </si>
-  <si>
-    <t>11.0%</t>
+    <t>11.6%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
   </si>
   <si>
     <t>10.3%</t>
   </si>
   <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.3%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>+762</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+975</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1036</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
     <t>9.8%</t>
   </si>
   <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
     <t>9.0%</t>
   </si>
   <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+871</t>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+890</t>
   </si>
   <si>
     <t>+920</t>
   </si>
   <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+975</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
     <t>+1011</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>+747</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+1024</t>
   </si>
 </sst>
 </file>
@@ -593,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -607,7 +604,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -621,7 +618,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -635,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -649,7 +646,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,7 +660,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -677,7 +674,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -691,7 +688,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,7 +702,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -716,10 +713,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -740,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -748,16 +745,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -768,122 +765,122 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -912,119 +909,119 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1038,16 +1035,16 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/Board Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -30,181 +30,196 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Flaccillionares</t>
+  </si>
+  <si>
     <t>Mystical Magical Moonbeam Mark</t>
   </si>
   <si>
     <t>I Am Peter Awabdeh</t>
   </si>
   <si>
+    <t>Amy Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Empire of NJ </t>
+  </si>
+  <si>
+    <t>Center for Student Diversity</t>
+  </si>
+  <si>
+    <t>Commies</t>
+  </si>
+  <si>
+    <t>Navy MUN</t>
+  </si>
+  <si>
     <t>bbbbbbbbbbbbbbbbbb</t>
   </si>
   <si>
-    <t>Flaccillionares</t>
-  </si>
-  <si>
-    <t>Center for Student Diversity</t>
-  </si>
-  <si>
     <t>Chris Evans Sweater</t>
   </si>
   <si>
-    <t xml:space="preserve">First Empire of NJ </t>
-  </si>
-  <si>
-    <t>Amy Gold</t>
-  </si>
-  <si>
-    <t>Navy MUN</t>
-  </si>
-  <si>
-    <t>Commies</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.4%</t>
-  </si>
-  <si>
-    <t>41.5%</t>
-  </si>
-  <si>
-    <t>40.9%</t>
-  </si>
-  <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
+    <t>42.5%</t>
+  </si>
+  <si>
+    <t>42.3%</t>
+  </si>
+  <si>
+    <t>41.3%</t>
+  </si>
+  <si>
+    <t>41.1%</t>
+  </si>
+  <si>
+    <t>40.6%</t>
   </si>
   <si>
     <t>39.3%</t>
   </si>
   <si>
-    <t>39.1%</t>
-  </si>
-  <si>
-    <t>39.0%</t>
-  </si>
-  <si>
-    <t>38.2%</t>
-  </si>
-  <si>
-    <t>+130</t>
-  </si>
-  <si>
-    <t>+141</t>
-  </si>
-  <si>
-    <t>+144</t>
-  </si>
-  <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+150</t>
+    <t>38.6%</t>
+  </si>
+  <si>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>38.1%</t>
+  </si>
+  <si>
+    <t>37.9%</t>
+  </si>
+  <si>
+    <t>+135</t>
+  </si>
+  <si>
+    <t>+136</t>
+  </si>
+  <si>
+    <t>+142</t>
+  </si>
+  <si>
+    <t>+143</t>
+  </si>
+  <si>
+    <t>+146</t>
   </si>
   <si>
     <t>+154</t>
   </si>
   <si>
-    <t>+156</t>
+    <t>+159</t>
+  </si>
+  <si>
+    <t>+161</t>
   </si>
   <si>
     <t>+162</t>
   </si>
   <si>
+    <t>+164</t>
+  </si>
+  <si>
     <t>Probability</t>
   </si>
   <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
     <t>11.6%</t>
   </si>
   <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
   </si>
   <si>
     <t>9.3%</t>
   </si>
   <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
+    <t>8.7%</t>
+  </si>
+  <si>
+    <t>8.1%</t>
   </si>
   <si>
     <t>+762</t>
   </si>
   <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+942</t>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+964</t>
   </si>
   <si>
     <t>+975</t>
   </si>
   <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+1076</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1011</t>
+    <t>+1049</t>
+  </si>
+  <si>
+    <t>+1135</t>
   </si>
 </sst>
 </file>
@@ -590,7 +605,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -604,7 +619,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -618,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -632,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -646,7 +661,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -660,7 +675,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -674,7 +689,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -688,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -702,7 +717,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -713,10 +728,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -745,16 +760,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -765,38 +780,38 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -807,80 +822,80 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -909,142 +924,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
